--- a/experiment/Wavlet_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/Wavlet_bestx4/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.59</v>
+        <v>33.64</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8923</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.25</v>
+        <v>34.47</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9373</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.13</v>
+        <v>28.28</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9071</v>
+        <v>0.9123</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.87</v>
+        <v>32.89</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7952</v>
+        <v>0.7957</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.28</v>
+        <v>30.37</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9074</v>
+        <v>0.9089</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.83</v>
+        <v>31.93</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8869</v>
+        <v>0.8893</v>
       </c>
     </row>
   </sheetData>
